--- a/untranslated/downloads/data-excel/3.1.2.xlsx
+++ b/untranslated/downloads/data-excel/3.1.2.xlsx
@@ -704,7 +704,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -714,7 +714,7 @@
     <col min="5" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
@@ -736,7 +736,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>30</v>
       </c>
@@ -758,7 +758,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="13"/>
       <c r="C3" s="12"/>
@@ -774,7 +774,7 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>35</v>
       </c>
@@ -832,8 +832,11 @@
       <c r="S4" s="26">
         <v>2022</v>
       </c>
+      <c r="T4" s="26">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>11</v>
       </c>
@@ -891,8 +894,11 @@
       <c r="S5" s="37">
         <v>99.5</v>
       </c>
+      <c r="T5" s="37">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -950,8 +956,11 @@
       <c r="S6" s="38">
         <v>99.358544044156048</v>
       </c>
+      <c r="T6" s="38">
+        <v>99.426175237254469</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
@@ -1009,8 +1018,11 @@
       <c r="S7" s="38">
         <v>99.400057479522914</v>
       </c>
+      <c r="T7" s="38">
+        <v>99.458151211935132</v>
+      </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>16</v>
       </c>
@@ -1068,8 +1080,11 @@
       <c r="S8" s="38">
         <v>99.513194978221875</v>
       </c>
+      <c r="T8" s="38">
+        <v>99.44178628389156</v>
+      </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
@@ -1127,8 +1142,11 @@
       <c r="S9" s="38">
         <v>99.232429839290006</v>
       </c>
+      <c r="T9" s="38">
+        <v>99.453125</v>
+      </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
@@ -1186,8 +1204,11 @@
       <c r="S10" s="38">
         <v>99.453093666824671</v>
       </c>
+      <c r="T10" s="38">
+        <v>99.487295483676391</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>21</v>
       </c>
@@ -1245,8 +1266,11 @@
       <c r="S11" s="38">
         <v>99.686258104998956</v>
       </c>
+      <c r="T11" s="38">
+        <v>99.743589743589752</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>23</v>
       </c>
@@ -1304,8 +1328,11 @@
       <c r="S12" s="38">
         <v>99.42525365081228</v>
       </c>
+      <c r="T12" s="38">
+        <v>99.190647482014398</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>25</v>
       </c>
@@ -1363,8 +1390,11 @@
       <c r="S13" s="38">
         <v>99.561275226674468</v>
       </c>
+      <c r="T13" s="38">
+        <v>99.483321247280642</v>
+      </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>28</v>
       </c>
@@ -1422,8 +1452,11 @@
       <c r="S14" s="39">
         <v>99.831561216970215</v>
       </c>
+      <c r="T14" s="39">
+        <v>99.771121504627331</v>
+      </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="O15" s="33"/>
     </row>
   </sheetData>
